--- a/output/graficos_dimensiones/comunal_d_env_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:14</t>
+    <t xml:space="preserve">2026-09-10 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:28</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>125.11</v>
+        <v>133.86</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>112.88</v>
+        <v>121.85</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>100.65</v>
+        <v>108.21</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>2018</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>68.5</v>
+        <v>73.24</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>58.7</v>
+        <v>62.42</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>57.54</v>
+        <v>61.62</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>54.37</v>
+        <v>58.56</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>47.72</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>43.75</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="11">
@@ -658,7 +658,7 @@
         <v>2018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>35.25</v>
+        <v>36.84</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:08</t>
+    <t xml:space="preserve">2026-10-02 15:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:42</t>
+    <t xml:space="preserve">2026-10-04 10:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:38</t>
+    <t xml:space="preserve">2026-10-05 16:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
